--- a/statistics_tables/variety_dtm_results.xlsx
+++ b/statistics_tables/variety_dtm_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">location</t>
   </si>
@@ -33,6 +33,12 @@
   </si>
   <si>
     <t xml:space="preserve">groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSD</t>
   </si>
   <si>
     <t xml:space="preserve">mean_group_se</t>
@@ -506,19 +512,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
         <v>2022</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>95.6203627977333</v>
@@ -527,33 +539,37 @@
         <v>0.460302246091958</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.310120239216446</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.56855032634804</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>95.7501252807587</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0372694063416035</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="n">
         <v>2022</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>95.178812398443</v>
@@ -562,33 +578,37 @@
         <v>0.796843144123695</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.310120239216446</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.56855032634804</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>95.7501252807587</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.0372694063416035</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
         <v>2022</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
         <v>96.4512006460996</v>
@@ -597,33 +617,37 @@
         <v>0.459063424892164</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.310120239216446</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.56855032634804</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>95.7501252807587</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.0372694063416035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>2023</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>93.8028690816235</v>
@@ -632,33 +656,37 @@
         <v>0.199229722997948</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.418839562453053</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="n">
         <v>1.08152217398096</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>93.690549098984</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.0115435567875511</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
         <v>2023</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>93.7726477411516</v>
@@ -667,33 +695,37 @@
         <v>0.161427650637425</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.418839562453053</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="n">
         <v>1.08152217398096</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>93.690549098984</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.0115435567875511</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
         <v>2023</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>93.496130474177</v>
@@ -702,33 +734,37 @@
         <v>0.178735779802309</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.418839562453053</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="n">
         <v>1.08152217398096</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>93.690549098984</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0115435567875511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" t="n">
         <v>2022</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
         <v>97.0177313929325</v>
@@ -737,33 +773,37 @@
         <v>0.34973803720902</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.823766089733147</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="n">
         <v>1.78761588866232</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>96.8660799332817</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0184545084295098</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="n">
         <v>2022</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>96.7742622718587</v>
@@ -772,33 +812,37 @@
         <v>0.339864531701532</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.823766089733147</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" t="n">
         <v>1.78761588866232</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>96.8660799332817</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.0184545084295098</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" t="n">
         <v>2022</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>96.806246135054</v>
@@ -807,33 +851,37 @@
         <v>0.180402431508649</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.823766089733147</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" t="n">
         <v>1.78761588866232</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>96.8660799332817</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.0184545084295098</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="n">
         <v>2023</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
         <v>82.3958251338164</v>
@@ -842,33 +890,37 @@
         <v>0.907724619537004</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.504154024339562</v>
+      </c>
+      <c r="I11"/>
+      <c r="J11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" t="n">
         <v>5.82181279904156</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>81.4901113801104</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.0714419541272404</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12" t="n">
         <v>2023</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>80.8434106091441</v>
@@ -877,33 +929,37 @@
         <v>0.888503861957905</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.504154024339562</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" t="n">
         <v>5.82181279904156</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>81.4901113801104</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.0714419541272404</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" t="n">
         <v>2023</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>81.2310983973708</v>
@@ -912,33 +968,37 @@
         <v>1.10794908519678</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.504154024339562</v>
+      </c>
+      <c r="I13"/>
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" t="n">
         <v>5.82181279904156</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>81.4901113801104</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>0.0714419541272404</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" t="n">
         <v>2024</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>91.9861111111111</v>
@@ -947,33 +1007,39 @@
         <v>0.364803769338335</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.00870132963941191</v>
       </c>
       <c r="I14" t="n">
+        <v>1.16042658151305</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.57334147793545</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>91.5657407407407</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.0281037586450767</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" t="n">
         <v>2024</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>92.2027777777778</v>
@@ -982,33 +1048,39 @@
         <v>0.374896517173826</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.00870132963941191</v>
       </c>
       <c r="I15" t="n">
+        <v>1.16042658151305</v>
+      </c>
+      <c r="J15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.57334147793545</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>91.5657407407407</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.0281037586450767</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" t="n">
         <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
         <v>90.5083333333333</v>
@@ -1017,33 +1089,39 @@
         <v>0.490033607529051</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.00870132963941191</v>
       </c>
       <c r="I16" t="n">
+        <v>1.16042658151305</v>
+      </c>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.57334147793545</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>91.5657407407407</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0281037586450767</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" t="n">
         <v>2022</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>94.1633311130194</v>
@@ -1052,33 +1130,37 @@
         <v>0.453713317144981</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.17224631464682</v>
+      </c>
+      <c r="I17"/>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.90637219072444</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>94.6334691575826</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0307118846703673</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" t="n">
         <v>2022</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
         <v>94.3707312671724</v>
@@ -1087,33 +1169,37 @@
         <v>0.452899207972733</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.17224631464682</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.90637219072444</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>94.6334691575826</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0307118846703673</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" t="n">
         <v>2022</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
         <v>95.366345092556</v>
@@ -1122,33 +1208,37 @@
         <v>0.531712049124244</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.17224631464682</v>
+      </c>
+      <c r="I19"/>
+      <c r="J19" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.90637219072444</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>94.6334691575826</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.0307118846703673</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" t="n">
         <v>2023</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>87.5849463337775</v>
@@ -1157,33 +1247,39 @@
         <v>0.428265300594193</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.000104980490601696</v>
       </c>
       <c r="I20" t="n">
+        <v>1.0259332061558</v>
+      </c>
+      <c r="J20" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" t="n">
         <v>2.37284870549016</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>87.7418386356664</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.0270435261260369</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B21" t="n">
         <v>2023</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>88.9698154237788</v>
@@ -1192,33 +1288,39 @@
         <v>0.26180002399689</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
+        <v>16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.000104980490601696</v>
       </c>
       <c r="I21" t="n">
+        <v>1.0259332061558</v>
+      </c>
+      <c r="J21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.37284870549016</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>87.7418386356664</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.0270435261260369</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="n">
         <v>2023</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
         <v>86.6707541494428</v>
@@ -1227,33 +1329,39 @@
         <v>0.386811277730243</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" t="s">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.000104980490601696</v>
       </c>
       <c r="I22" t="n">
+        <v>1.0259332061558</v>
+      </c>
+      <c r="J22" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.37284870549016</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>87.7418386356664</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.0270435261260369</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B23" t="n">
         <v>2024</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
         <v>101.913288870026</v>
@@ -1262,33 +1370,37 @@
         <v>0.628894242741452</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" t="n">
+        <v>16</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.466315587039841</v>
+      </c>
+      <c r="I23"/>
+      <c r="J23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.65765409855909</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>101.670822653835</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0359754549347213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" t="n">
         <v>2024</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
         <v>102.042263228673</v>
@@ -1297,33 +1409,37 @@
         <v>0.736416009821743</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24" t="n">
+        <v>16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.466315587039841</v>
+      </c>
+      <c r="I24"/>
+      <c r="J24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.65765409855909</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>101.670822653835</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.0359754549347213</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" t="n">
         <v>2024</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
         <v>101.056915862807</v>
@@ -1332,18 +1448,22 @@
         <v>0.42649602456295</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.466315587039841</v>
+      </c>
+      <c r="I25"/>
+      <c r="J25" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.65765409855909</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>101.670822653835</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0359754549347213</v>
       </c>
     </row>
